--- a/backend/prisma/data/sample_deals_30.xlsx
+++ b/backend/prisma/data/sample_deals_30.xlsx
@@ -43,10 +43,10 @@
     <t>علت باخت (در صورت باخت)</t>
   </si>
   <si>
-    <t>البرز تعمیرگاه</t>
-  </si>
-  <si>
-    <t>تعمیرگاه مستقل کوچک</t>
+    <t>البرز پیمانکاری</t>
+  </si>
+  <si>
+    <t>پیمانکار مستقل کوچک</t>
   </si>
   <si>
     <t>تهران</t>
@@ -64,7 +64,7 @@
     <t/>
   </si>
   <si>
-    <t>رادین تعمیرگاه</t>
+    <t>رادین پیمانکاری</t>
   </si>
   <si>
     <t>کرج</t>
@@ -76,25 +76,25 @@
     <t>سارا محمدی</t>
   </si>
   <si>
-    <t>ارس گروه تعمیرگاهی</t>
-  </si>
-  <si>
-    <t>تعمیرگاه زنجیره‌ای بزرگ</t>
+    <t>ارس گروه بازرگانی</t>
+  </si>
+  <si>
+    <t>فروشگاه زنجیره‌ای بزرگ</t>
   </si>
   <si>
     <t>پارسیان حمل و نقل</t>
   </si>
   <si>
-    <t>ناوگان صنعتی/شرکتی</t>
-  </si>
-  <si>
-    <t>نمایشگاه صنعت خودرو</t>
+    <t>خریدار صنعتی/شرکتی</t>
+  </si>
+  <si>
+    <t>نمایشگاه صنعت</t>
   </si>
   <si>
     <t>حسین کریمی</t>
   </si>
   <si>
-    <t>یکتا گروه تعمیرگاهی</t>
+    <t>یکتا گروه بازرگانی</t>
   </si>
   <si>
     <t>تبریز</t>
@@ -103,10 +103,10 @@
     <t>معرفی مشتری قبلی</t>
   </si>
   <si>
-    <t>ماهان اتوسرویس</t>
-  </si>
-  <si>
-    <t>تعمیرگاه مستقل متوسط</t>
+    <t>ماهان خدمات فنی</t>
+  </si>
+  <si>
+    <t>پیمانکار مستقل متوسط</t>
   </si>
   <si>
     <t>وبسایت/اینستاگرام</t>
@@ -118,103 +118,103 @@
     <t>زمان تحویل با نیاز مشتری همخوانی نداشت</t>
   </si>
   <si>
-    <t>آرین اتوسرویس</t>
+    <t>آرین خدمات فنی</t>
   </si>
   <si>
     <t>شیراز</t>
   </si>
   <si>
-    <t>گلستان تعمیرگاه</t>
+    <t>گلستان پیمانکاری</t>
   </si>
   <si>
     <t>حجم خرید برای شرایط اعتباری ما کم بود</t>
   </si>
   <si>
-    <t>صدرا تعمیرگاه</t>
+    <t>صدرا پیمانکاری</t>
   </si>
   <si>
     <t>مشتری برند رقیب ارزان‌تر انتخاب کرد</t>
   </si>
   <si>
-    <t>پویا پخش قطعات</t>
-  </si>
-  <si>
-    <t>پخش‌کننده قطعات یدکی</t>
-  </si>
-  <si>
-    <t>گلستان گروه تعمیرگاهی</t>
-  </si>
-  <si>
-    <t>بهار تعمیرگاه</t>
+    <t>پویا توزیع تجهیزات</t>
+  </si>
+  <si>
+    <t>توزیع‌کننده منطقه‌ای</t>
+  </si>
+  <si>
+    <t>گلستان گروه بازرگانی</t>
+  </si>
+  <si>
+    <t>بهار پیمانکاری</t>
   </si>
   <si>
     <t>مشهد</t>
   </si>
   <si>
-    <t>رادین گروه تعمیرگاهی</t>
-  </si>
-  <si>
-    <t>کارون اتوسرویس</t>
-  </si>
-  <si>
-    <t>پویا نمایندگی خودرو</t>
-  </si>
-  <si>
-    <t>نمایندگی رسمی خودرو</t>
+    <t>رادین گروه بازرگانی</t>
+  </si>
+  <si>
+    <t>کارون خدمات فنی</t>
+  </si>
+  <si>
+    <t>پویا نمایندگی رسمی</t>
+  </si>
+  <si>
+    <t>نماینده رسمی برند</t>
   </si>
   <si>
     <t>اهواز</t>
   </si>
   <si>
-    <t>کیان نمایندگی خودرو</t>
-  </si>
-  <si>
-    <t>توس گروه تعمیرگاهی</t>
-  </si>
-  <si>
-    <t>آرین تعمیرگاه</t>
+    <t>کیان نمایندگی رسمی</t>
+  </si>
+  <si>
+    <t>توس گروه بازرگانی</t>
+  </si>
+  <si>
+    <t>آرین پیمانکاری</t>
   </si>
   <si>
     <t>مشتری به کیفیت شک داشت و نمونه کافی نبود</t>
   </si>
   <si>
-    <t>بهار اتوسرویس</t>
+    <t>بهار خدمات فنی</t>
   </si>
   <si>
     <t>قم</t>
   </si>
   <si>
-    <t>سپهر نمایندگی خودرو</t>
-  </si>
-  <si>
-    <t>کیان گروه تعمیرگاهی</t>
-  </si>
-  <si>
-    <t>الوند گروه تعمیرگاهی</t>
-  </si>
-  <si>
-    <t>البرز پخش قطعات</t>
-  </si>
-  <si>
-    <t>مهر گروه تعمیرگاهی</t>
+    <t>سپهر نمایندگی رسمی</t>
+  </si>
+  <si>
+    <t>کیان گروه بازرگانی</t>
+  </si>
+  <si>
+    <t>الوند گروه بازرگانی</t>
+  </si>
+  <si>
+    <t>البرز توزیع تجهیزات</t>
+  </si>
+  <si>
+    <t>مهر گروه بازرگانی</t>
   </si>
   <si>
     <t>آریا حمل و نقل</t>
   </si>
   <si>
-    <t>الوند تعمیرگاه</t>
+    <t>الوند پیمانکاری</t>
   </si>
   <si>
     <t>قیمت بالاتر از بودجه مشتری بود</t>
   </si>
   <si>
-    <t>نوین پخش قطعات</t>
-  </si>
-  <si>
-    <t>رادین پخش قطعات</t>
-  </si>
-  <si>
-    <t>سبلان گروه تعمیرگاهی</t>
+    <t>نوین توزیع تجهیزات</t>
+  </si>
+  <si>
+    <t>رادین توزیع تجهیزات</t>
+  </si>
+  <si>
+    <t>سبلان گروه بازرگانی</t>
   </si>
   <si>
     <t>اصفهان</t>
